--- a/front/public/excel/deliveryNoteTemplate.xlsx
+++ b/front/public/excel/deliveryNoteTemplate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tcshd365.sharepoint.com/sites/msteams_e9d089-WG/Shared Documents/人材開発推進WG/30_新人教育/2025年度/販売管理システム/販売管理システムExcelテンプレート/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:1_{6C669B5C-2D13-4978-B3F1-635DFCC575F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E8625C3-1FFD-44A4-BC71-F1D110BBA5A9}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{6C669B5C-2D13-4978-B3F1-635DFCC575F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62B98F14-617B-498C-9ED8-200AC7BB8976}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-7125" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="納品書" sheetId="1" r:id="rId1"/>
@@ -883,8 +883,7 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="2" max="2" width="39.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="39.25" customWidth="1"/>
-    <col min="5" max="5" width="27.4140625" customWidth="1"/>
+    <col min="3" max="5" width="39.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1053,7 +1052,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="49" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="49" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1068,8 +1067,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100531F82A73EE04949B92C893AA9ED3D8B" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="9410a1db6c4108f6da538e5e9d46e9dc">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18ad70a2-d0c6-4b98-b594-e1471017f0f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="554750112bcaa4f1e868a2b7404a37fc" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100531F82A73EE04949B92C893AA9ED3D8B" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="f8f69b03f9575f720a8435decfb1b23e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="18ad70a2-d0c6-4b98-b594-e1471017f0f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b653dc9858a0a3cf05c7e3a1316d1aee" ns2:_="">
     <xsd:import namespace="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -1257,35 +1256,21 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77BFA079-FFC5-49EE-A815-5D7FAE3DACE7}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E9A8A5-EB48-4975-9777-D88F922B6C6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="18ad70a2-d0c6-4b98-b594-e1471017f0f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45DC7E57-9D62-49CF-8DB9-0FCF2AAA45C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
